--- a/docs/tabulka-radost.xlsx
+++ b/docs/tabulka-radost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vutbr-my.sharepoint.com/personal/267991_vutbr_cz/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AADA8F95-3977-4E6A-A2D1-19E58C371993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E112788A-36B2-4163-B036-BE2D42D4B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
   </bookViews>
@@ -39,37 +39,267 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Mám se dobře</t>
-  </si>
-  <si>
-    <t>Dnes je krásný den</t>
-  </si>
-  <si>
-    <t>Mám radostný den</t>
-  </si>
-  <si>
-    <t>Venku svítí slunce</t>
-  </si>
-  <si>
-    <t>Jsem šťastný</t>
-  </si>
-  <si>
-    <t>Usmívám se celý den</t>
-  </si>
-  <si>
-    <t>Život je krásný</t>
-  </si>
-  <si>
-    <t>Srdce mi zpívá</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Mám/- se/. do/. bře/.</t>
+  </si>
+  <si>
+    <t>Dnes/. je/. krá/- sný/- den/.</t>
+  </si>
+  <si>
+    <t>Ven/. ku/. sví/- tí/- slun/. ce/.</t>
+  </si>
+  <si>
+    <t>Jsem/. šťast/. ný/-</t>
+  </si>
+  <si>
+    <t>Us/. mí/- vám/- se/. ce/. lý/- den/.</t>
+  </si>
+  <si>
+    <t>Ahoj</t>
+  </si>
+  <si>
+    <t>A/. hoj/.</t>
+  </si>
+  <si>
+    <t>To/. je/. su/. per/.</t>
+  </si>
+  <si>
+    <t>Mám/. tě/. rád/-</t>
+  </si>
+  <si>
+    <t>To/. se/. mi/. lí/- bí/-</t>
+  </si>
+  <si>
+    <t>U/. dě/. lal/. jsi/. mi/. ra/. dost/.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mám se </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dobře</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>To</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se mi líbí</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dnes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> je </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>krásný</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> den</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Venku </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>svítí</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> slunce</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jsem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> šťastný</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Usmívám se </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>celý</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> den</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Udělal jsi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> radost</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mám tě </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rád</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To je </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>super</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +309,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -106,9 +344,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -443,46 +682,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7CE48D-FAAF-45DE-B902-65A6BD5016E2}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>7</v>
       </c>
     </row>

--- a/docs/tabulka-radost.xlsx
+++ b/docs/tabulka-radost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E112788A-36B2-4163-B036-BE2D42D4B4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C6F5B-4ED6-47EB-A0F2-C306D77F2585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
+    <workbookView xWindow="-26355" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -65,9 +65,6 @@
     <t>To/. je/. su/. per/.</t>
   </si>
   <si>
-    <t>Mám/. tě/. rád/-</t>
-  </si>
-  <si>
     <t>To/. se/. mi/. lí/- bí/-</t>
   </si>
   <si>
@@ -293,6 +290,9 @@
       </rPr>
       <t>super</t>
     </r>
+  </si>
+  <si>
+    <t>Mám/- tě/. rád/-</t>
   </si>
 </sst>
 </file>
@@ -690,7 +690,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -706,15 +706,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -738,18 +738,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -762,7 +762,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>

--- a/docs/tabulka-radost.xlsx
+++ b/docs/tabulka-radost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C6F5B-4ED6-47EB-A0F2-C306D77F2585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB643D94-436C-4EE3-8E91-060AE299C4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26355" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
+    <workbookView xWindow="-24465" yWindow="3975" windowWidth="21600" windowHeight="11385" xr2:uid="{F919D72D-6EEA-46E4-BD17-FBF57A672A1B}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -41,21 +41,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>Mám/- se/. do/. bře/.</t>
-  </si>
-  <si>
-    <t>Dnes/. je/. krá/- sný/- den/.</t>
-  </si>
-  <si>
     <t>Ven/. ku/. sví/- tí/- slun/. ce/.</t>
   </si>
   <si>
     <t>Jsem/. šťast/. ný/-</t>
   </si>
   <si>
-    <t>Us/. mí/- vám/- se/. ce/. lý/- den/.</t>
-  </si>
-  <si>
     <t>Ahoj</t>
   </si>
   <si>
@@ -293,6 +284,15 @@
   </si>
   <si>
     <t>Mám/- tě/. rád/-</t>
+  </si>
+  <si>
+    <t>Mám/- se/. dob/. ře/.</t>
+  </si>
+  <si>
+    <t>Dnes/. je/. krás/- ný/- den/.</t>
+  </si>
+  <si>
+    <t>U/. smí/- vám/- se/. ce/. lý/- den/.</t>
   </si>
 </sst>
 </file>
@@ -690,82 +690,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
